--- a/regression/TilapiaFish_6mo.xlsx
+++ b/regression/TilapiaFish_6mo.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Fishfiles\all regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC6A0E7-029E-480D-B2F4-54B272ED83EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="4600" windowHeight="4100"/>
+    <workbookView xWindow="696" yWindow="4020" windowWidth="22188" windowHeight="12528" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="7">
   <si>
     <t>NO.of Fish</t>
   </si>
@@ -32,16 +33,10 @@
     <t>Weight/g</t>
   </si>
   <si>
-    <t xml:space="preserve">Length/cm </t>
-  </si>
-  <si>
     <t>Width/cm</t>
   </si>
   <si>
     <t>Length/cm</t>
-  </si>
-  <si>
-    <t>Five fish were placed in one tank</t>
   </si>
   <si>
     <t>16,5</t>
@@ -56,7 +51,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -74,7 +69,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,18 +88,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -118,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -129,14 +112,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -420,61 +395,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="G2:AA69"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.81640625" customWidth="1"/>
-    <col min="8" max="8" width="14.08984375" customWidth="1"/>
-    <col min="9" max="9" width="10.08984375" customWidth="1"/>
-    <col min="10" max="10" width="12.7265625" customWidth="1"/>
-    <col min="11" max="11" width="11.6328125" customWidth="1"/>
-    <col min="12" max="12" width="7.6328125" customWidth="1"/>
-    <col min="13" max="13" width="11.08984375" customWidth="1"/>
-    <col min="14" max="14" width="10.54296875" customWidth="1"/>
-    <col min="15" max="15" width="11.81640625" customWidth="1"/>
-    <col min="16" max="16" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" customWidth="1"/>
+    <col min="15" max="15" width="11.77734375" customWidth="1"/>
+    <col min="16" max="16" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="7:27" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="K2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="7"/>
-      <c r="U2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-    </row>
-    <row r="3" spans="7:27" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="7:27" ht="18" x14ac:dyDescent="0.35">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="4"/>
+      <c r="U2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="7:27" x14ac:dyDescent="0.35">
-      <c r="L4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>3</v>
-      </c>
+    </row>
+    <row r="4" spans="7:27" x14ac:dyDescent="0.3">
       <c r="S4" s="3" t="s">
         <v>0</v>
       </c>
@@ -482,10 +432,10 @@
         <v>1</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="3" t="s">
@@ -495,25 +445,13 @@
         <v>1</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="7:27" x14ac:dyDescent="0.35">
-      <c r="L5" s="4">
-        <v>1</v>
-      </c>
-      <c r="M5" s="4">
-        <v>76</v>
-      </c>
-      <c r="N5" s="4">
-        <v>17</v>
-      </c>
-      <c r="O5" s="4">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="7:27" x14ac:dyDescent="0.3">
       <c r="S5" s="2">
         <v>1</v>
       </c>
@@ -540,19 +478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="7:27" x14ac:dyDescent="0.35">
-      <c r="L6" s="4">
-        <v>2</v>
-      </c>
-      <c r="M6" s="4">
-        <v>72</v>
-      </c>
-      <c r="N6" s="4">
-        <v>16</v>
-      </c>
-      <c r="O6" s="4">
-        <v>5</v>
-      </c>
+    <row r="6" spans="7:27" x14ac:dyDescent="0.3">
       <c r="S6" s="2">
         <v>2</v>
       </c>
@@ -579,19 +505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="7:27" x14ac:dyDescent="0.35">
-      <c r="L7" s="4">
-        <v>3</v>
-      </c>
-      <c r="M7" s="4">
-        <v>76</v>
-      </c>
-      <c r="N7" s="4">
-        <v>16.5</v>
-      </c>
-      <c r="O7" s="4">
-        <v>5</v>
-      </c>
+    <row r="7" spans="7:27" x14ac:dyDescent="0.3">
       <c r="S7" s="2">
         <v>3</v>
       </c>
@@ -618,19 +532,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="8" spans="7:27" x14ac:dyDescent="0.35">
-      <c r="L8" s="4">
-        <v>4</v>
-      </c>
-      <c r="M8" s="4">
-        <v>62</v>
-      </c>
-      <c r="N8" s="4">
-        <v>15</v>
-      </c>
-      <c r="O8" s="4">
-        <v>5</v>
-      </c>
+    <row r="8" spans="7:27" x14ac:dyDescent="0.3">
       <c r="S8" s="2">
         <v>4</v>
       </c>
@@ -657,19 +559,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="9" spans="7:27" x14ac:dyDescent="0.35">
-      <c r="L9" s="4">
-        <v>5</v>
-      </c>
-      <c r="M9" s="4">
-        <v>76</v>
-      </c>
-      <c r="N9" s="4">
-        <v>15.5</v>
-      </c>
-      <c r="O9" s="4">
-        <v>5</v>
-      </c>
+    <row r="9" spans="7:27" x14ac:dyDescent="0.3">
       <c r="S9" s="2">
         <v>5</v>
       </c>
@@ -696,7 +586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G10" s="1"/>
       <c r="S10" s="2">
         <v>6</v>
@@ -724,7 +614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G11" s="1"/>
       <c r="S11" s="2">
         <v>7</v>
@@ -752,7 +642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G12" s="1"/>
       <c r="S12" s="2">
         <v>8</v>
@@ -780,7 +670,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="13" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G13" s="1"/>
       <c r="S13" s="2">
         <v>9</v>
@@ -808,7 +698,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="14" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G14" s="1"/>
       <c r="S14" s="2">
         <v>10</v>
@@ -836,7 +726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G15" s="1"/>
       <c r="S15" s="2">
         <v>11</v>
@@ -864,7 +754,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G16" s="1"/>
       <c r="S16" s="2">
         <v>12</v>
@@ -892,7 +782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G17" s="1"/>
       <c r="S17" s="2">
         <v>13</v>
@@ -920,7 +810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G18" s="1"/>
       <c r="S18" s="2">
         <v>14</v>
@@ -948,7 +838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G19" s="1"/>
       <c r="S19" s="2">
         <v>15</v>
@@ -976,7 +866,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="20" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G20" s="1"/>
       <c r="S20" s="2">
         <v>16</v>
@@ -1004,7 +894,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="21" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G21" s="1"/>
       <c r="S21" s="2">
         <v>17</v>
@@ -1032,7 +922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G22" s="1"/>
       <c r="S22" s="2">
         <v>18</v>
@@ -1060,7 +950,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="23" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G23" s="1"/>
       <c r="S23" s="2">
         <v>19</v>
@@ -1088,7 +978,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="24" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G24" s="1"/>
       <c r="S24" s="2">
         <v>20</v>
@@ -1116,7 +1006,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="25" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
@@ -1128,7 +1018,7 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G26" s="1"/>
       <c r="S26" s="3" t="s">
         <v>0</v>
@@ -1137,10 +1027,10 @@
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W26" s="1"/>
       <c r="X26" s="3" t="s">
@@ -1150,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="Z26" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="7:27" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G27" s="1"/>
       <c r="S27" s="2">
         <v>41</v>
@@ -1184,7 +1074,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="28" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G28" s="1"/>
       <c r="S28" s="2">
         <v>42</v>
@@ -1212,7 +1102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G29" s="1"/>
       <c r="S29" s="2">
         <v>43</v>
@@ -1240,7 +1130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G30" s="1"/>
       <c r="S30" s="2">
         <v>44</v>
@@ -1268,7 +1158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G31" s="1"/>
       <c r="S31" s="2">
         <v>45</v>
@@ -1296,7 +1186,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="32" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G32" s="1"/>
       <c r="S32" s="2">
         <v>46</v>
@@ -1324,7 +1214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="33" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G33" s="1"/>
       <c r="S33" s="2">
         <v>47</v>
@@ -1336,7 +1226,7 @@
         <v>13.5</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W33" s="1"/>
       <c r="X33" s="2">
@@ -1352,7 +1242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="34" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G34" s="1"/>
       <c r="S34" s="2">
         <v>48</v>
@@ -1380,7 +1270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="35" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G35" s="1"/>
       <c r="S35" s="2">
         <v>49</v>
@@ -1408,7 +1298,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="36" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="36" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G36" s="1"/>
       <c r="S36" s="2">
         <v>50</v>
@@ -1436,7 +1326,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="37" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="37" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G37" s="1"/>
       <c r="S37" s="2">
         <v>51</v>
@@ -1464,7 +1354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="38" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G38" s="1"/>
       <c r="S38" s="2">
         <v>52</v>
@@ -1492,7 +1382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="39" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G39" s="1"/>
       <c r="S39" s="2">
         <v>53</v>
@@ -1520,7 +1410,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="40" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="40" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G40" s="1"/>
       <c r="S40" s="2">
         <v>54</v>
@@ -1548,7 +1438,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="41" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="41" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G41" s="1"/>
       <c r="S41" s="2">
         <v>55</v>
@@ -1576,7 +1466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="42" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G42" s="1"/>
       <c r="S42" s="2">
         <v>56</v>
@@ -1604,7 +1494,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="43" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="43" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G43" s="1"/>
       <c r="S43" s="2">
         <v>57</v>
@@ -1632,7 +1522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="44" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G44" s="1"/>
       <c r="S44" s="2">
         <v>58</v>
@@ -1660,7 +1550,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="45" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="45" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G45" s="1"/>
       <c r="S45" s="2">
         <v>59</v>
@@ -1688,7 +1578,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="46" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="46" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G46" s="1"/>
       <c r="S46" s="2">
         <v>60</v>
@@ -1716,7 +1606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="47" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
@@ -1728,7 +1618,7 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
     </row>
-    <row r="48" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="48" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G48" s="1"/>
       <c r="S48" s="3" t="s">
         <v>0</v>
@@ -1737,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
@@ -1748,7 +1638,7 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
     </row>
-    <row r="49" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="49" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G49" s="1"/>
       <c r="S49" s="2">
         <v>81</v>
@@ -1768,7 +1658,7 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
     </row>
-    <row r="50" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="50" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G50" s="1"/>
       <c r="S50" s="2">
         <v>82</v>
@@ -1788,7 +1678,7 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
     </row>
-    <row r="51" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="51" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G51" s="1"/>
       <c r="S51" s="2">
         <v>83</v>
@@ -1808,7 +1698,7 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
     </row>
-    <row r="52" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="52" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G52" s="1"/>
       <c r="S52" s="2">
         <v>84</v>
@@ -1828,7 +1718,7 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
     </row>
-    <row r="53" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="53" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G53" s="1"/>
       <c r="S53" s="2">
         <v>85</v>
@@ -1848,7 +1738,7 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
     </row>
-    <row r="54" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="54" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G54" s="1"/>
       <c r="S54" s="2">
         <v>86</v>
@@ -1868,7 +1758,7 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
     </row>
-    <row r="55" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="55" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G55" s="1"/>
       <c r="S55" s="2">
         <v>87</v>
@@ -1888,7 +1778,7 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
     </row>
-    <row r="56" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="56" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G56" s="1"/>
       <c r="S56" s="2">
         <v>88</v>
@@ -1908,7 +1798,7 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
     </row>
-    <row r="57" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="57" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G57" s="1"/>
       <c r="S57" s="2">
         <v>89</v>
@@ -1928,7 +1818,7 @@
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
     </row>
-    <row r="58" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="58" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G58" s="1"/>
       <c r="S58" s="2">
         <v>90</v>
@@ -1948,7 +1838,7 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="59" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G59" s="1"/>
       <c r="S59" s="2">
         <v>91</v>
@@ -1968,7 +1858,7 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
     </row>
-    <row r="60" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="60" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G60" s="1"/>
       <c r="S60" s="2">
         <v>92</v>
@@ -1988,7 +1878,7 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
-    <row r="61" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="61" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G61" s="1"/>
       <c r="S61" s="2">
         <v>93</v>
@@ -1997,7 +1887,7 @@
         <v>78</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V61" s="2">
         <v>5.5</v>
@@ -2008,7 +1898,7 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
     </row>
-    <row r="62" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="62" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G62" s="1"/>
       <c r="S62" s="2">
         <v>94</v>
@@ -2028,7 +1918,7 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
     </row>
-    <row r="63" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="63" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G63" s="1"/>
       <c r="S63" s="2">
         <v>95</v>
@@ -2048,7 +1938,7 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
     </row>
-    <row r="64" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="64" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G64" s="1"/>
       <c r="S64" s="2">
         <v>96</v>
@@ -2068,7 +1958,7 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
     </row>
-    <row r="65" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="65" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G65" s="1"/>
       <c r="S65" s="2">
         <v>97</v>
@@ -2088,7 +1978,7 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
     </row>
-    <row r="66" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="66" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G66" s="1"/>
       <c r="S66" s="2">
         <v>98</v>
@@ -2108,7 +1998,7 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
     </row>
-    <row r="67" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="67" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G67" s="1"/>
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
@@ -2116,7 +2006,7 @@
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
     </row>
-    <row r="68" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="68" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G68" s="1"/>
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
@@ -2124,7 +2014,7 @@
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
     </row>
-    <row r="69" spans="7:27" x14ac:dyDescent="0.35">
+    <row r="69" spans="7:27" x14ac:dyDescent="0.3">
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
